--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91805</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R9" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B10" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R10" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B9" t="n">
-        <v>91808</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R9" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R10" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R9" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B10" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R10" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B9" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R9" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R10" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R9" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B10" t="n">
-        <v>91811</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R10" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,7 +1596,7 @@
         <v>129065049</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R9" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>91818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R10" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>91825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R9" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B10" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R10" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>129065093</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129065049</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R9" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R10" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R9" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R10" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129065140</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B9" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R9" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R10" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065093</v>
+        <v>129065084</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603290</v>
+        <v>603281</v>
       </c>
       <c r="R9" t="n">
-        <v>7000253</v>
+        <v>7000236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1460,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B10" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1497,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R10" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118853563</v>
+        <v>118853562</v>
       </c>
       <c r="B2" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603258</v>
+        <v>603207</v>
       </c>
       <c r="R2" t="n">
-        <v>7000356</v>
+        <v>7000446</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118853559</v>
+        <v>118853564</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603288</v>
+        <v>603258</v>
       </c>
       <c r="R3" t="n">
-        <v>7000589</v>
+        <v>7000356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118853560</v>
+        <v>129065084</v>
       </c>
       <c r="B4" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäckingesbäcken, Ång</t>
+          <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603232</v>
+        <v>603281</v>
       </c>
       <c r="R4" t="n">
-        <v>7000548</v>
+        <v>7000236</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118853562</v>
+        <v>129065140</v>
       </c>
       <c r="B5" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäckingesbäcken, Ång</t>
+          <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603207</v>
+        <v>603276</v>
       </c>
       <c r="R5" t="n">
-        <v>7000446</v>
+        <v>7000272</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,12 +1066,7 @@
         <v>118853566</v>
       </c>
       <c r="B6" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118853564</v>
+        <v>129064982</v>
       </c>
       <c r="B7" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1171,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäckingesbäcken, Ång</t>
+          <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603258</v>
+        <v>603288</v>
       </c>
       <c r="R7" t="n">
-        <v>7000356</v>
+        <v>7000193</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1230,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,62 +1255,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118853561</v>
+        <v>129065049</v>
       </c>
       <c r="B8" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bäckingesbäcken, Ång</t>
+          <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603212</v>
+        <v>603294</v>
       </c>
       <c r="R8" t="n">
-        <v>7000520</v>
+        <v>7000215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1337,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,22 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065084</v>
+        <v>129065093</v>
       </c>
       <c r="B9" t="n">
-        <v>91851</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603281</v>
+        <v>603290</v>
       </c>
       <c r="R9" t="n">
-        <v>7000236</v>
+        <v>7000253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,6 +1450,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,50 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065093</v>
+        <v>118853560</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällberget, Ång</t>
+          <t>Bäckingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603290</v>
+        <v>603232</v>
       </c>
       <c r="R10" t="n">
-        <v>7000253</v>
+        <v>7000548</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,17 +1546,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,62 +1566,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129065049</v>
+        <v>118853561</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällberget, Ång</t>
+          <t>Bäckingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603294</v>
+        <v>603212</v>
       </c>
       <c r="R11" t="n">
-        <v>7000215</v>
+        <v>7000520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,17 +1643,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,22 +1663,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129065140</v>
+        <v>118853559</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,34 +1686,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällberget, Ång</t>
+          <t>Bäckingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603276</v>
+        <v>603288</v>
       </c>
       <c r="R12" t="n">
-        <v>7000272</v>
+        <v>7000589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1740,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,12 +1760,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 45692-2025 artfynd.xlsx
+++ b/artfynd/A 45692-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853559</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853562</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853564</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065084</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065140</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853566</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064982</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065049</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065093</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853560</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,8 +1824,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853561</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>